--- a/samples/예시데이터_Integrated_Order_Status_wk38_분석.xlsx
+++ b/samples/예시데이터_Integrated_Order_Status_wk38_분석.xlsx
@@ -906,7 +906,87 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>엔진</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HCE</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>46100</v>
+      </c>
+      <c r="D12">
+        <v>520070</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>M261300090</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PLANT-A</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>EXE-9009</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>EX900</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>EXE-9009</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ENG-A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Engine Assy</t>
+        </is>
+      </c>
+      <c r="L12">
+        <v>80070</v>
+      </c>
       <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12">
+        <v>46270</v>
+      </c>
+      <c r="O12">
+        <v>46285</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>OCEAN</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Tier4</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Undispatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="M13">
         <v>45</v>
       </c>
     </row>
